--- a/static/data/exports/Retro_HP_AE_2012.xlsx
+++ b/static/data/exports/Retro_HP_AE_2012.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,6 +576,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>29</v>
+      </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
@@ -638,8 +651,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>64</v>
+      </c>
       <c r="Q3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>13</v>
@@ -700,6 +726,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>37</v>
+      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -762,6 +801,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>65</v>
+      </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
@@ -824,6 +876,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>48</v>
+      </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
@@ -886,6 +951,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>41</v>
+      </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
@@ -948,6 +1026,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>41</v>
+      </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
@@ -1010,6 +1101,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>61</v>
+      </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
@@ -1072,8 +1176,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>65</v>
+      </c>
       <c r="Q10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>13</v>
@@ -1134,6 +1251,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>60</v>
+      </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
@@ -1196,6 +1326,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>39</v>
+      </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
@@ -1258,6 +1401,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>67</v>
+      </c>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
@@ -1320,6 +1476,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>26</v>
+      </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
@@ -1382,6 +1551,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>50</v>
+      </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
@@ -1444,6 +1626,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>41</v>
+      </c>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
@@ -1506,6 +1701,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>37</v>
+      </c>
       <c r="Q17" t="b">
         <v>0</v>
       </c>
@@ -1568,6 +1776,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>57</v>
+      </c>
       <c r="Q18" t="b">
         <v>0</v>
       </c>
@@ -1630,8 +1851,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>63</v>
+      </c>
       <c r="Q19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>13</v>
@@ -1692,6 +1926,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>60</v>
+      </c>
       <c r="Q20" t="b">
         <v>0</v>
       </c>
@@ -1754,6 +2001,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>38</v>
+      </c>
       <c r="Q21" t="b">
         <v>0</v>
       </c>
@@ -1816,6 +2076,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>38</v>
+      </c>
       <c r="Q22" t="b">
         <v>0</v>
       </c>
@@ -1878,6 +2151,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>51</v>
+      </c>
       <c r="Q23" t="b">
         <v>0</v>
       </c>
@@ -1940,8 +2226,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>55</v>
+      </c>
       <c r="Q24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>13</v>
@@ -2002,6 +2301,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>67</v>
+      </c>
       <c r="Q25" t="b">
         <v>0</v>
       </c>
@@ -2064,6 +2376,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>39</v>
+      </c>
       <c r="Q26" t="b">
         <v>0</v>
       </c>
@@ -2126,6 +2451,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>47</v>
+      </c>
       <c r="Q27" t="b">
         <v>0</v>
       </c>
@@ -2188,6 +2526,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>73</v>
+      </c>
       <c r="Q28" t="b">
         <v>0</v>
       </c>
@@ -2250,6 +2601,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>54</v>
+      </c>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
@@ -2312,8 +2676,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>48</v>
+      </c>
       <c r="Q30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>13</v>
@@ -2374,6 +2751,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>33</v>
+      </c>
       <c r="Q31" t="b">
         <v>0</v>
       </c>
@@ -2436,6 +2826,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>47</v>
+      </c>
       <c r="Q32" t="b">
         <v>0</v>
       </c>
@@ -2498,6 +2901,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>59</v>
+      </c>
       <c r="Q33" t="b">
         <v>0</v>
       </c>
@@ -2560,6 +2976,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>55</v>
+      </c>
       <c r="Q34" t="b">
         <v>0</v>
       </c>
@@ -2622,6 +3051,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>58</v>
+      </c>
       <c r="Q35" t="b">
         <v>0</v>
       </c>
@@ -2684,6 +3126,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>36</v>
+      </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
@@ -2746,6 +3201,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>39</v>
+      </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
@@ -2808,6 +3276,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>64</v>
+      </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
@@ -2870,6 +3351,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>53</v>
+      </c>
       <c r="Q39" t="b">
         <v>0</v>
       </c>
@@ -2932,6 +3426,19 @@
           <t>BHBP</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>29</v>
+      </c>
       <c r="Q40" t="b">
         <v>0</v>
       </c>
@@ -2994,8 +3501,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>71</v>
+      </c>
       <c r="Q41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>13</v>
@@ -3056,6 +3576,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>43</v>
+      </c>
       <c r="Q42" t="b">
         <v>0</v>
       </c>
@@ -3118,6 +3651,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>52</v>
+      </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
@@ -3180,6 +3726,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>35</v>
+      </c>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
@@ -3242,6 +3801,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>53</v>
+      </c>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
@@ -3304,6 +3876,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>54</v>
+      </c>
       <c r="Q46" t="b">
         <v>0</v>
       </c>
@@ -3366,6 +3951,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>36</v>
+      </c>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
@@ -3428,6 +4026,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>38</v>
+      </c>
       <c r="Q48" t="b">
         <v>0</v>
       </c>
@@ -3490,8 +4101,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>34</v>
+      </c>
       <c r="Q49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
         <v>13</v>
@@ -3552,6 +4176,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>49</v>
+      </c>
       <c r="Q50" t="b">
         <v>0</v>
       </c>
@@ -3588,7 +4225,7 @@
         <v>10924</v>
       </c>
       <c r="F51" t="n">
-        <v>19.07888991739</v>
+        <v>19.07888992</v>
       </c>
       <c r="G51" t="n">
         <v>3</v>
@@ -3613,6 +4250,19 @@
         <is>
           <t>IND</t>
         </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>50</v>
       </c>
       <c r="Q51" t="b">
         <v>0</v>
@@ -3676,6 +4326,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>46</v>
+      </c>
       <c r="Q52" t="b">
         <v>0</v>
       </c>
@@ -3738,6 +4401,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>47</v>
+      </c>
       <c r="Q53" t="b">
         <v>0</v>
       </c>
@@ -3800,6 +4476,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>39</v>
+      </c>
       <c r="Q54" t="b">
         <v>0</v>
       </c>
@@ -3862,6 +4551,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>32</v>
+      </c>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
@@ -3924,6 +4626,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>54</v>
+      </c>
       <c r="Q56" t="b">
         <v>0</v>
       </c>
@@ -3986,6 +4701,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>63</v>
+      </c>
       <c r="Q57" t="b">
         <v>0</v>
       </c>
@@ -4048,8 +4776,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>57</v>
+      </c>
       <c r="Q58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
         <v>13</v>
@@ -4110,8 +4851,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>77</v>
+      </c>
       <c r="Q59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
         <v>13</v>
@@ -4172,6 +4926,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>58</v>
+      </c>
       <c r="Q60" t="b">
         <v>0</v>
       </c>
@@ -4234,6 +5001,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>55</v>
+      </c>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
@@ -4296,6 +5076,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>42</v>
+      </c>
       <c r="Q62" t="b">
         <v>0</v>
       </c>
@@ -4358,6 +5151,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>39</v>
+      </c>
       <c r="Q63" t="b">
         <v>0</v>
       </c>
@@ -4420,6 +5226,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>71</v>
+      </c>
       <c r="Q64" t="b">
         <v>0</v>
       </c>
@@ -4482,6 +5301,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>29</v>
+      </c>
       <c r="Q65" t="b">
         <v>0</v>
       </c>
@@ -4544,6 +5376,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>35</v>
+      </c>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
@@ -4606,6 +5451,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>44</v>
+      </c>
       <c r="Q67" t="b">
         <v>0</v>
       </c>
@@ -4668,6 +5526,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>44</v>
+      </c>
       <c r="Q68" t="b">
         <v>0</v>
       </c>
@@ -4730,6 +5601,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>41</v>
+      </c>
       <c r="Q69" t="b">
         <v>0</v>
       </c>
@@ -4792,6 +5676,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>47</v>
+      </c>
       <c r="Q70" t="b">
         <v>0</v>
       </c>
@@ -4854,6 +5751,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>48</v>
+      </c>
       <c r="Q71" t="b">
         <v>0</v>
       </c>
@@ -4916,6 +5826,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>40</v>
+      </c>
       <c r="Q72" t="b">
         <v>0</v>
       </c>
@@ -4978,6 +5901,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>40</v>
+      </c>
       <c r="Q73" t="b">
         <v>0</v>
       </c>
@@ -5040,6 +5976,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>48</v>
+      </c>
       <c r="Q74" t="b">
         <v>0</v>
       </c>
@@ -5102,8 +6051,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>57</v>
+      </c>
       <c r="Q75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
         <v>13</v>
@@ -5164,6 +6126,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>35</v>
+      </c>
       <c r="Q76" t="b">
         <v>0</v>
       </c>
@@ -5226,6 +6201,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>42</v>
+      </c>
       <c r="Q77" t="b">
         <v>0</v>
       </c>
@@ -5288,6 +6276,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>37</v>
+      </c>
       <c r="Q78" t="b">
         <v>0</v>
       </c>
@@ -5350,6 +6351,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>63</v>
+      </c>
       <c r="Q79" t="b">
         <v>0</v>
       </c>
@@ -5412,6 +6426,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>61</v>
+      </c>
       <c r="Q80" t="b">
         <v>0</v>
       </c>
@@ -5474,6 +6501,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>61</v>
+      </c>
       <c r="Q81" t="b">
         <v>0</v>
       </c>
@@ -5536,6 +6576,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>49</v>
+      </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
@@ -5598,8 +6651,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>61</v>
+      </c>
       <c r="Q83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" t="n">
         <v>13</v>
@@ -5660,6 +6726,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>62</v>
+      </c>
       <c r="Q84" t="b">
         <v>0</v>
       </c>
@@ -5722,6 +6801,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>60</v>
+      </c>
       <c r="Q85" t="b">
         <v>0</v>
       </c>
@@ -5784,6 +6876,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>60</v>
+      </c>
       <c r="Q86" t="b">
         <v>0</v>
       </c>
@@ -5846,6 +6951,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>26</v>
+      </c>
       <c r="Q87" t="b">
         <v>0</v>
       </c>
@@ -5908,8 +7026,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>78</v>
+      </c>
       <c r="Q88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" t="n">
         <v>13</v>
@@ -5970,6 +7101,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>51</v>
+      </c>
       <c r="Q89" t="b">
         <v>0</v>
       </c>
@@ -6032,6 +7176,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>62</v>
+      </c>
       <c r="Q90" t="b">
         <v>0</v>
       </c>
@@ -6094,6 +7251,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>44</v>
+      </c>
       <c r="Q91" t="b">
         <v>0</v>
       </c>
@@ -6156,6 +7326,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>51</v>
+      </c>
       <c r="Q92" t="b">
         <v>0</v>
       </c>
@@ -6218,6 +7401,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>60</v>
+      </c>
       <c r="Q93" t="b">
         <v>0</v>
       </c>
@@ -6280,6 +7476,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>29</v>
+      </c>
       <c r="Q94" t="b">
         <v>0</v>
       </c>
@@ -6342,6 +7551,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>40</v>
+      </c>
       <c r="Q95" t="b">
         <v>0</v>
       </c>
@@ -6404,6 +7626,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>58</v>
+      </c>
       <c r="Q96" t="b">
         <v>0</v>
       </c>
@@ -6466,8 +7701,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>49</v>
+      </c>
       <c r="Q97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" t="n">
         <v>13</v>
@@ -6528,6 +7776,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>55</v>
+      </c>
       <c r="Q98" t="b">
         <v>0</v>
       </c>
@@ -6590,6 +7851,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>43</v>
+      </c>
       <c r="Q99" t="b">
         <v>0</v>
       </c>
@@ -6652,6 +7926,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>67</v>
+      </c>
       <c r="Q100" t="b">
         <v>0</v>
       </c>
@@ -6714,6 +8001,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>31</v>
+      </c>
       <c r="Q101" t="b">
         <v>0</v>
       </c>
@@ -6776,6 +8076,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>28</v>
+      </c>
       <c r="Q102" t="b">
         <v>0</v>
       </c>
@@ -6838,6 +8151,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>61</v>
+      </c>
       <c r="Q103" t="b">
         <v>0</v>
       </c>
@@ -6900,8 +8226,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>58</v>
+      </c>
       <c r="Q104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="n">
         <v>13</v>
@@ -6962,6 +8301,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>48</v>
+      </c>
       <c r="Q105" t="b">
         <v>0</v>
       </c>
@@ -7024,6 +8376,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>52</v>
+      </c>
       <c r="Q106" t="b">
         <v>0</v>
       </c>
@@ -7086,6 +8451,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>55</v>
+      </c>
       <c r="Q107" t="b">
         <v>0</v>
       </c>
@@ -7148,6 +8526,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>57</v>
+      </c>
       <c r="Q108" t="b">
         <v>0</v>
       </c>
@@ -7210,6 +8601,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>70</v>
+      </c>
       <c r="Q109" t="b">
         <v>0</v>
       </c>
@@ -7272,6 +8676,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>57</v>
+      </c>
       <c r="Q110" t="b">
         <v>0</v>
       </c>
@@ -7334,6 +8751,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>30</v>
+      </c>
       <c r="Q111" t="b">
         <v>0</v>
       </c>
@@ -7370,7 +8800,7 @@
         <v>14632</v>
       </c>
       <c r="F112" t="n">
-        <v>28.99894960065</v>
+        <v>28.9989496</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -7395,6 +8825,19 @@
         <is>
           <t>IND</t>
         </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>38</v>
       </c>
       <c r="Q112" t="b">
         <v>0</v>
@@ -7458,6 +8901,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>58</v>
+      </c>
       <c r="Q113" t="b">
         <v>0</v>
       </c>
@@ -7520,8 +8976,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>46</v>
+      </c>
       <c r="Q114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" t="n">
         <v>13</v>
@@ -7582,6 +9051,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>46</v>
+      </c>
       <c r="Q115" t="b">
         <v>0</v>
       </c>
@@ -7644,6 +9126,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>36</v>
+      </c>
       <c r="Q116" t="b">
         <v>0</v>
       </c>
@@ -7706,6 +9201,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>56</v>
+      </c>
       <c r="Q117" t="b">
         <v>0</v>
       </c>
@@ -7768,6 +9276,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>51</v>
+      </c>
       <c r="Q118" t="b">
         <v>0</v>
       </c>
@@ -7830,6 +9351,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>38</v>
+      </c>
       <c r="Q119" t="b">
         <v>0</v>
       </c>
@@ -7892,8 +9426,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>47</v>
+      </c>
       <c r="Q120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" t="n">
         <v>13</v>
@@ -7954,6 +9501,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>72</v>
+      </c>
       <c r="Q121" t="b">
         <v>0</v>
       </c>
@@ -8016,6 +9576,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>60</v>
+      </c>
       <c r="Q122" t="b">
         <v>0</v>
       </c>
@@ -8078,6 +9651,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>43</v>
+      </c>
       <c r="Q123" t="b">
         <v>0</v>
       </c>
@@ -8140,6 +9726,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>59</v>
+      </c>
       <c r="Q124" t="b">
         <v>0</v>
       </c>
@@ -8202,6 +9801,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>37</v>
+      </c>
       <c r="Q125" t="b">
         <v>0</v>
       </c>
@@ -8264,6 +9876,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>43</v>
+      </c>
       <c r="Q126" t="b">
         <v>0</v>
       </c>
@@ -8326,8 +9951,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>40</v>
+      </c>
       <c r="Q127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" t="n">
         <v>13</v>
@@ -8388,8 +10026,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>61</v>
+      </c>
       <c r="Q128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R128" t="n">
         <v>13</v>
@@ -8450,6 +10101,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>49</v>
+      </c>
       <c r="Q129" t="b">
         <v>0</v>
       </c>
@@ -8512,6 +10176,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>56</v>
+      </c>
       <c r="Q130" t="b">
         <v>0</v>
       </c>
@@ -8574,6 +10251,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>40</v>
+      </c>
       <c r="Q131" t="b">
         <v>0</v>
       </c>
@@ -8636,6 +10326,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>58</v>
+      </c>
       <c r="Q132" t="b">
         <v>0</v>
       </c>
@@ -8698,6 +10401,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>62</v>
+      </c>
       <c r="Q133" t="b">
         <v>0</v>
       </c>
@@ -8760,6 +10476,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>47</v>
+      </c>
       <c r="Q134" t="b">
         <v>0</v>
       </c>
@@ -8822,6 +10551,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>59</v>
+      </c>
       <c r="Q135" t="b">
         <v>0</v>
       </c>
@@ -8884,6 +10626,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>48</v>
+      </c>
       <c r="Q136" t="b">
         <v>0</v>
       </c>
@@ -8946,6 +10701,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>36</v>
+      </c>
       <c r="Q137" t="b">
         <v>0</v>
       </c>
@@ -9008,6 +10776,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>34</v>
+      </c>
       <c r="Q138" t="b">
         <v>0</v>
       </c>
@@ -9070,6 +10851,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>51</v>
+      </c>
       <c r="Q139" t="b">
         <v>0</v>
       </c>
@@ -9132,6 +10926,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>41</v>
+      </c>
       <c r="Q140" t="b">
         <v>0</v>
       </c>
@@ -9194,6 +11001,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>71</v>
+      </c>
       <c r="Q141" t="b">
         <v>0</v>
       </c>
@@ -9256,8 +11076,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>46</v>
+      </c>
       <c r="Q142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" t="n">
         <v>13</v>
@@ -9318,6 +11151,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>53</v>
+      </c>
       <c r="Q143" t="b">
         <v>0</v>
       </c>
@@ -9380,6 +11226,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>43</v>
+      </c>
       <c r="Q144" t="b">
         <v>0</v>
       </c>
@@ -9442,6 +11301,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>51</v>
+      </c>
       <c r="Q145" t="b">
         <v>0</v>
       </c>
@@ -9504,6 +11376,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>54</v>
+      </c>
       <c r="Q146" t="b">
         <v>0</v>
       </c>
@@ -9566,6 +11451,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>75</v>
+      </c>
       <c r="Q147" t="b">
         <v>0</v>
       </c>
@@ -9628,6 +11526,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>51</v>
+      </c>
       <c r="Q148" t="b">
         <v>0</v>
       </c>
@@ -9690,6 +11601,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>33</v>
+      </c>
       <c r="Q149" t="b">
         <v>0</v>
       </c>
@@ -9752,6 +11676,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>65</v>
+      </c>
       <c r="Q150" t="b">
         <v>0</v>
       </c>
@@ -9814,6 +11751,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>42</v>
+      </c>
       <c r="Q151" t="b">
         <v>0</v>
       </c>
@@ -9876,6 +11826,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>65</v>
+      </c>
       <c r="Q152" t="b">
         <v>0</v>
       </c>
@@ -9938,6 +11901,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>33</v>
+      </c>
       <c r="Q153" t="b">
         <v>0</v>
       </c>
@@ -10000,6 +11976,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>32</v>
+      </c>
       <c r="Q154" t="b">
         <v>0</v>
       </c>
@@ -10062,6 +12051,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>25</v>
+      </c>
       <c r="Q155" t="b">
         <v>0</v>
       </c>
@@ -10124,6 +12126,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>32</v>
+      </c>
       <c r="Q156" t="b">
         <v>0</v>
       </c>
@@ -10186,6 +12201,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>30</v>
+      </c>
       <c r="Q157" t="b">
         <v>0</v>
       </c>
@@ -10248,6 +12276,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>50</v>
+      </c>
       <c r="Q158" t="b">
         <v>0</v>
       </c>
@@ -10310,8 +12351,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>47</v>
+      </c>
       <c r="Q159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R159" t="n">
         <v>13</v>
@@ -10372,6 +12426,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>51</v>
+      </c>
       <c r="Q160" t="b">
         <v>0</v>
       </c>
@@ -10434,6 +12501,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>42</v>
+      </c>
       <c r="Q161" t="b">
         <v>0</v>
       </c>
@@ -10496,6 +12576,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>29</v>
+      </c>
       <c r="Q162" t="b">
         <v>0</v>
       </c>
@@ -10558,6 +12651,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>58</v>
+      </c>
       <c r="Q163" t="b">
         <v>0</v>
       </c>
@@ -10620,8 +12726,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>44</v>
+      </c>
       <c r="Q164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R164" t="n">
         <v>13</v>
@@ -10682,6 +12801,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>38</v>
+      </c>
       <c r="Q165" t="b">
         <v>0</v>
       </c>
@@ -10744,6 +12876,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>63</v>
+      </c>
       <c r="Q166" t="b">
         <v>0</v>
       </c>
@@ -10806,6 +12951,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>56</v>
+      </c>
       <c r="Q167" t="b">
         <v>0</v>
       </c>
@@ -10868,6 +13026,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>64</v>
+      </c>
       <c r="Q168" t="b">
         <v>0</v>
       </c>
@@ -10930,6 +13101,19 @@
           <t>IJP</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>52</v>
+      </c>
       <c r="Q169" t="b">
         <v>0</v>
       </c>
@@ -10992,6 +13176,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>63</v>
+      </c>
       <c r="Q170" t="b">
         <v>0</v>
       </c>
@@ -11054,6 +13251,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>52</v>
+      </c>
       <c r="Q171" t="b">
         <v>0</v>
       </c>
@@ -11116,6 +13326,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>47</v>
+      </c>
       <c r="Q172" t="b">
         <v>0</v>
       </c>
@@ -11178,6 +13401,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>56</v>
+      </c>
       <c r="Q173" t="b">
         <v>0</v>
       </c>
@@ -11240,6 +13476,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>43</v>
+      </c>
       <c r="Q174" t="b">
         <v>0</v>
       </c>
@@ -11302,6 +13551,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>42</v>
+      </c>
       <c r="Q175" t="b">
         <v>0</v>
       </c>
@@ -11364,6 +13626,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>55</v>
+      </c>
       <c r="Q176" t="b">
         <v>0</v>
       </c>
@@ -11426,8 +13701,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>63</v>
+      </c>
       <c r="Q177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R177" t="n">
         <v>13</v>
@@ -11488,6 +13776,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>40</v>
+      </c>
       <c r="Q178" t="b">
         <v>0</v>
       </c>
@@ -11550,6 +13851,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>76</v>
+      </c>
       <c r="Q179" t="b">
         <v>0</v>
       </c>
@@ -11612,6 +13926,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>29</v>
+      </c>
       <c r="Q180" t="b">
         <v>0</v>
       </c>
@@ -11674,6 +14001,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>59</v>
+      </c>
       <c r="Q181" t="b">
         <v>0</v>
       </c>
@@ -11736,8 +14076,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>42</v>
+      </c>
       <c r="Q182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R182" t="n">
         <v>13</v>
@@ -11798,6 +14151,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>39</v>
+      </c>
       <c r="Q183" t="b">
         <v>0</v>
       </c>
@@ -11860,6 +14226,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>72</v>
+      </c>
       <c r="Q184" t="b">
         <v>0</v>
       </c>
@@ -11922,6 +14301,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>49</v>
+      </c>
       <c r="Q185" t="b">
         <v>0</v>
       </c>
@@ -11984,6 +14376,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>71</v>
+      </c>
       <c r="Q186" t="b">
         <v>0</v>
       </c>
@@ -12046,8 +14451,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>46</v>
+      </c>
       <c r="Q187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R187" t="n">
         <v>13</v>
@@ -12108,6 +14526,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>66</v>
+      </c>
       <c r="Q188" t="b">
         <v>0</v>
       </c>
@@ -12170,6 +14601,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>44</v>
+      </c>
       <c r="Q189" t="b">
         <v>0</v>
       </c>
@@ -12232,6 +14676,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>46</v>
+      </c>
       <c r="Q190" t="b">
         <v>0</v>
       </c>
@@ -12294,6 +14751,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>54</v>
+      </c>
       <c r="Q191" t="b">
         <v>0</v>
       </c>
@@ -12356,8 +14826,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>64</v>
+      </c>
       <c r="Q192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R192" t="n">
         <v>13</v>
@@ -12418,6 +14901,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>38</v>
+      </c>
       <c r="Q193" t="b">
         <v>0</v>
       </c>
@@ -12480,6 +14976,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>56</v>
+      </c>
       <c r="Q194" t="b">
         <v>0</v>
       </c>
@@ -12542,6 +15051,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>37</v>
+      </c>
       <c r="Q195" t="b">
         <v>0</v>
       </c>
@@ -12604,6 +15126,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>32</v>
+      </c>
       <c r="Q196" t="b">
         <v>0</v>
       </c>
@@ -12666,6 +15201,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>67</v>
+      </c>
       <c r="Q197" t="b">
         <v>0</v>
       </c>
@@ -12728,6 +15276,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>47</v>
+      </c>
       <c r="Q198" t="b">
         <v>0</v>
       </c>
@@ -12790,6 +15351,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>49</v>
+      </c>
       <c r="Q199" t="b">
         <v>0</v>
       </c>
@@ -12852,6 +15426,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>47</v>
+      </c>
       <c r="Q200" t="b">
         <v>0</v>
       </c>
@@ -12914,6 +15501,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>43</v>
+      </c>
       <c r="Q201" t="b">
         <v>0</v>
       </c>
@@ -12976,8 +15576,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>47</v>
+      </c>
       <c r="Q202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R202" t="n">
         <v>13</v>
@@ -13038,6 +15651,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P203" t="n">
+        <v>50</v>
+      </c>
       <c r="Q203" t="b">
         <v>0</v>
       </c>
@@ -13100,6 +15726,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>41</v>
+      </c>
       <c r="Q204" t="b">
         <v>0</v>
       </c>
@@ -13162,6 +15801,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>55</v>
+      </c>
       <c r="Q205" t="b">
         <v>0</v>
       </c>
@@ -13224,8 +15876,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>67</v>
+      </c>
       <c r="Q206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R206" t="n">
         <v>13</v>
@@ -13286,6 +15951,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>58</v>
+      </c>
       <c r="Q207" t="b">
         <v>0</v>
       </c>
@@ -13348,6 +16026,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>45</v>
+      </c>
       <c r="Q208" t="b">
         <v>0</v>
       </c>
@@ -13410,6 +16101,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>31</v>
+      </c>
       <c r="Q209" t="b">
         <v>0</v>
       </c>
@@ -13472,6 +16176,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>45</v>
+      </c>
       <c r="Q210" t="b">
         <v>0</v>
       </c>
@@ -13534,6 +16251,19 @@
           <t>BHBP</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>29</v>
+      </c>
       <c r="Q211" t="b">
         <v>0</v>
       </c>
@@ -13596,8 +16326,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>64</v>
+      </c>
       <c r="Q212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R212" t="n">
         <v>13</v>
@@ -13658,6 +16401,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>52</v>
+      </c>
       <c r="Q213" t="b">
         <v>0</v>
       </c>
@@ -13720,6 +16476,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>29</v>
+      </c>
       <c r="Q214" t="b">
         <v>0</v>
       </c>
@@ -13782,6 +16551,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>43</v>
+      </c>
       <c r="Q215" t="b">
         <v>0</v>
       </c>
@@ -13844,6 +16626,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>61</v>
+      </c>
       <c r="Q216" t="b">
         <v>0</v>
       </c>
@@ -13906,6 +16701,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P217" t="n">
+        <v>54</v>
+      </c>
       <c r="Q217" t="b">
         <v>0</v>
       </c>
@@ -13968,6 +16776,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>71</v>
+      </c>
       <c r="Q218" t="b">
         <v>0</v>
       </c>
@@ -14030,6 +16851,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>41</v>
+      </c>
       <c r="Q219" t="b">
         <v>0</v>
       </c>
@@ -14092,8 +16926,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>61</v>
+      </c>
       <c r="Q220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R220" t="n">
         <v>13</v>
@@ -14154,6 +17001,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>39</v>
+      </c>
       <c r="Q221" t="b">
         <v>0</v>
       </c>
@@ -14216,6 +17076,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>29</v>
+      </c>
       <c r="Q222" t="b">
         <v>0</v>
       </c>
@@ -14278,6 +17151,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>51</v>
+      </c>
       <c r="Q223" t="b">
         <v>0</v>
       </c>
@@ -14340,6 +17226,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>65</v>
+      </c>
       <c r="Q224" t="b">
         <v>0</v>
       </c>
@@ -14402,6 +17301,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>42</v>
+      </c>
       <c r="Q225" t="b">
         <v>0</v>
       </c>
@@ -14464,6 +17376,19 @@
           <t>HND</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>71</v>
+      </c>
       <c r="Q226" t="b">
         <v>0</v>
       </c>
@@ -14526,8 +17451,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>56</v>
+      </c>
       <c r="Q227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R227" t="n">
         <v>13</v>
@@ -14588,6 +17526,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>64</v>
+      </c>
       <c r="Q228" t="b">
         <v>0</v>
       </c>
@@ -14650,6 +17601,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>43</v>
+      </c>
       <c r="Q229" t="b">
         <v>0</v>
       </c>
@@ -14712,6 +17676,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>52</v>
+      </c>
       <c r="Q230" t="b">
         <v>0</v>
       </c>
@@ -14774,6 +17751,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>39</v>
+      </c>
       <c r="Q231" t="b">
         <v>0</v>
       </c>
@@ -14836,6 +17826,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>46</v>
+      </c>
       <c r="Q232" t="b">
         <v>0</v>
       </c>
@@ -14898,6 +17901,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>55</v>
+      </c>
       <c r="Q233" t="b">
         <v>0</v>
       </c>
@@ -14960,6 +17976,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>55</v>
+      </c>
       <c r="Q234" t="b">
         <v>0</v>
       </c>
@@ -15022,6 +18051,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>39</v>
+      </c>
       <c r="Q235" t="b">
         <v>0</v>
       </c>
@@ -15084,6 +18126,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>37</v>
+      </c>
       <c r="Q236" t="b">
         <v>0</v>
       </c>
@@ -15146,8 +18201,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>50</v>
+      </c>
       <c r="Q237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R237" t="n">
         <v>13</v>
@@ -15208,8 +18276,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P238" t="n">
+        <v>50</v>
+      </c>
       <c r="Q238" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R238" t="n">
         <v>13</v>
@@ -15270,6 +18351,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>68</v>
+      </c>
       <c r="Q239" t="b">
         <v>0</v>
       </c>
@@ -15332,6 +18426,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P240" t="n">
+        <v>41</v>
+      </c>
       <c r="Q240" t="b">
         <v>0</v>
       </c>
@@ -15394,6 +18501,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>56</v>
+      </c>
       <c r="Q241" t="b">
         <v>0</v>
       </c>
@@ -15456,6 +18576,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P242" t="n">
+        <v>63</v>
+      </c>
       <c r="Q242" t="b">
         <v>0</v>
       </c>
@@ -15518,6 +18651,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P243" t="n">
+        <v>64</v>
+      </c>
       <c r="Q243" t="b">
         <v>0</v>
       </c>
@@ -15580,6 +18726,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P244" t="n">
+        <v>46</v>
+      </c>
       <c r="Q244" t="b">
         <v>0</v>
       </c>
@@ -15642,6 +18801,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P245" t="n">
+        <v>42</v>
+      </c>
       <c r="Q245" t="b">
         <v>0</v>
       </c>
@@ -15704,8 +18876,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P246" t="n">
+        <v>68</v>
+      </c>
       <c r="Q246" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R246" t="n">
         <v>13</v>
@@ -15766,6 +18951,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P247" t="n">
+        <v>65</v>
+      </c>
       <c r="Q247" t="b">
         <v>0</v>
       </c>
@@ -15828,6 +19026,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P248" t="n">
+        <v>48</v>
+      </c>
       <c r="Q248" t="b">
         <v>0</v>
       </c>
@@ -15890,6 +19101,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P249" t="n">
+        <v>58</v>
+      </c>
       <c r="Q249" t="b">
         <v>0</v>
       </c>
@@ -15952,6 +19176,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P250" t="n">
+        <v>67</v>
+      </c>
       <c r="Q250" t="b">
         <v>0</v>
       </c>
@@ -16014,6 +19251,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P251" t="n">
+        <v>38</v>
+      </c>
       <c r="Q251" t="b">
         <v>0</v>
       </c>
@@ -16076,6 +19326,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P252" t="n">
+        <v>59</v>
+      </c>
       <c r="Q252" t="b">
         <v>0</v>
       </c>
@@ -16138,6 +19401,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P253" t="n">
+        <v>61</v>
+      </c>
       <c r="Q253" t="b">
         <v>0</v>
       </c>
@@ -16200,6 +19476,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P254" t="n">
+        <v>55</v>
+      </c>
       <c r="Q254" t="b">
         <v>0</v>
       </c>
@@ -16262,8 +19551,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P255" t="n">
+        <v>77</v>
+      </c>
       <c r="Q255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R255" t="n">
         <v>13</v>
@@ -16324,6 +19626,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P256" t="n">
+        <v>48</v>
+      </c>
       <c r="Q256" t="b">
         <v>0</v>
       </c>
@@ -16386,6 +19701,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P257" t="n">
+        <v>38</v>
+      </c>
       <c r="Q257" t="b">
         <v>0</v>
       </c>
@@ -16448,6 +19776,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P258" t="n">
+        <v>44</v>
+      </c>
       <c r="Q258" t="b">
         <v>0</v>
       </c>
@@ -16510,6 +19851,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P259" t="n">
+        <v>65</v>
+      </c>
       <c r="Q259" t="b">
         <v>0</v>
       </c>
@@ -16572,6 +19926,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>46</v>
+      </c>
       <c r="Q260" t="b">
         <v>0</v>
       </c>
@@ -16634,6 +20001,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>59</v>
+      </c>
       <c r="Q261" t="b">
         <v>0</v>
       </c>
@@ -16696,8 +20076,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>53</v>
+      </c>
       <c r="Q262" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R262" t="n">
         <v>13</v>
@@ -16758,6 +20151,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P263" t="n">
+        <v>46</v>
+      </c>
       <c r="Q263" t="b">
         <v>0</v>
       </c>
@@ -16820,6 +20226,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>42</v>
+      </c>
       <c r="Q264" t="b">
         <v>0</v>
       </c>
@@ -16882,6 +20301,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P265" t="n">
+        <v>47</v>
+      </c>
       <c r="Q265" t="b">
         <v>0</v>
       </c>
@@ -16944,6 +20376,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>32</v>
+      </c>
       <c r="Q266" t="b">
         <v>0</v>
       </c>
@@ -17006,8 +20451,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>68</v>
+      </c>
       <c r="Q267" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R267" t="n">
         <v>13</v>
@@ -17068,6 +20526,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>54</v>
+      </c>
       <c r="Q268" t="b">
         <v>0</v>
       </c>
@@ -17130,6 +20601,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>29</v>
+      </c>
       <c r="Q269" t="b">
         <v>0</v>
       </c>
@@ -17192,6 +20676,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P270" t="n">
+        <v>37</v>
+      </c>
       <c r="Q270" t="b">
         <v>0</v>
       </c>
@@ -17254,6 +20751,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P271" t="n">
+        <v>40</v>
+      </c>
       <c r="Q271" t="b">
         <v>0</v>
       </c>
@@ -17316,6 +20826,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>32</v>
+      </c>
       <c r="Q272" t="b">
         <v>0</v>
       </c>
@@ -17378,6 +20901,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P273" t="n">
+        <v>33</v>
+      </c>
       <c r="Q273" t="b">
         <v>0</v>
       </c>
@@ -17440,6 +20976,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P274" t="n">
+        <v>50</v>
+      </c>
       <c r="Q274" t="b">
         <v>0</v>
       </c>
@@ -17502,8 +21051,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P275" t="n">
+        <v>53</v>
+      </c>
       <c r="Q275" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R275" t="n">
         <v>13</v>
@@ -17564,6 +21126,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P276" t="n">
+        <v>44</v>
+      </c>
       <c r="Q276" t="b">
         <v>0</v>
       </c>
@@ -17626,6 +21201,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>53</v>
+      </c>
       <c r="Q277" t="b">
         <v>0</v>
       </c>
@@ -17688,6 +21276,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P278" t="n">
+        <v>57</v>
+      </c>
       <c r="Q278" t="b">
         <v>0</v>
       </c>
@@ -17750,6 +21351,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P279" t="n">
+        <v>44</v>
+      </c>
       <c r="Q279" t="b">
         <v>0</v>
       </c>
@@ -17812,6 +21426,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P280" t="n">
+        <v>47</v>
+      </c>
       <c r="Q280" t="b">
         <v>0</v>
       </c>
@@ -17874,6 +21501,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P281" t="n">
+        <v>45</v>
+      </c>
       <c r="Q281" t="b">
         <v>0</v>
       </c>
@@ -17936,8 +21576,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>48</v>
+      </c>
       <c r="Q282" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R282" t="n">
         <v>13</v>
@@ -17998,6 +21651,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P283" t="n">
+        <v>74</v>
+      </c>
       <c r="Q283" t="b">
         <v>0</v>
       </c>
@@ -18060,6 +21726,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P284" t="n">
+        <v>62</v>
+      </c>
       <c r="Q284" t="b">
         <v>0</v>
       </c>
@@ -18122,8 +21801,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P285" t="n">
+        <v>49</v>
+      </c>
       <c r="Q285" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R285" t="n">
         <v>13</v>
@@ -18184,6 +21876,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P286" t="n">
+        <v>62</v>
+      </c>
       <c r="Q286" t="b">
         <v>0</v>
       </c>
@@ -18246,6 +21951,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P287" t="n">
+        <v>54</v>
+      </c>
       <c r="Q287" t="b">
         <v>0</v>
       </c>
@@ -18308,6 +22026,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>50</v>
+      </c>
       <c r="Q288" t="b">
         <v>0</v>
       </c>
@@ -18370,6 +22101,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>57</v>
+      </c>
       <c r="Q289" t="b">
         <v>0</v>
       </c>
@@ -18432,8 +22176,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P290" t="n">
+        <v>44</v>
+      </c>
       <c r="Q290" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R290" t="n">
         <v>13</v>
@@ -18494,6 +22251,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P291" t="n">
+        <v>42</v>
+      </c>
       <c r="Q291" t="b">
         <v>0</v>
       </c>
@@ -18556,6 +22326,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P292" t="n">
+        <v>36</v>
+      </c>
       <c r="Q292" t="b">
         <v>0</v>
       </c>
@@ -18618,6 +22401,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P293" t="n">
+        <v>45</v>
+      </c>
       <c r="Q293" t="b">
         <v>0</v>
       </c>
@@ -18680,6 +22476,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>45</v>
+      </c>
       <c r="Q294" t="b">
         <v>0</v>
       </c>
@@ -18742,6 +22551,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P295" t="n">
+        <v>42</v>
+      </c>
       <c r="Q295" t="b">
         <v>0</v>
       </c>
@@ -18804,6 +22626,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P296" t="n">
+        <v>58</v>
+      </c>
       <c r="Q296" t="b">
         <v>0</v>
       </c>
@@ -18866,6 +22701,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P297" t="n">
+        <v>67</v>
+      </c>
       <c r="Q297" t="b">
         <v>0</v>
       </c>
@@ -18928,6 +22776,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P298" t="n">
+        <v>49</v>
+      </c>
       <c r="Q298" t="b">
         <v>0</v>
       </c>
@@ -18990,6 +22851,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P299" t="n">
+        <v>48</v>
+      </c>
       <c r="Q299" t="b">
         <v>0</v>
       </c>
@@ -19052,8 +22926,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P300" t="n">
+        <v>50</v>
+      </c>
       <c r="Q300" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R300" t="n">
         <v>13</v>
@@ -19114,6 +23001,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P301" t="n">
+        <v>43</v>
+      </c>
       <c r="Q301" t="b">
         <v>0</v>
       </c>
@@ -19176,6 +23076,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P302" t="n">
+        <v>43</v>
+      </c>
       <c r="Q302" t="b">
         <v>0</v>
       </c>
@@ -19238,6 +23151,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P303" t="n">
+        <v>46</v>
+      </c>
       <c r="Q303" t="b">
         <v>0</v>
       </c>
@@ -19300,6 +23226,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P304" t="n">
+        <v>57</v>
+      </c>
       <c r="Q304" t="b">
         <v>0</v>
       </c>
@@ -19362,8 +23301,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P305" t="n">
+        <v>48</v>
+      </c>
       <c r="Q305" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R305" t="n">
         <v>13</v>
@@ -19424,6 +23376,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>42</v>
+      </c>
       <c r="Q306" t="b">
         <v>0</v>
       </c>
@@ -19486,6 +23451,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>71</v>
+      </c>
       <c r="Q307" t="b">
         <v>0</v>
       </c>
@@ -19548,6 +23526,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
+        <v>61</v>
+      </c>
       <c r="Q308" t="b">
         <v>0</v>
       </c>
@@ -19610,6 +23601,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>36</v>
+      </c>
       <c r="Q309" t="b">
         <v>0</v>
       </c>
@@ -19672,6 +23676,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P310" t="n">
+        <v>66</v>
+      </c>
       <c r="Q310" t="b">
         <v>0</v>
       </c>
@@ -19734,8 +23751,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P311" t="n">
+        <v>48</v>
+      </c>
       <c r="Q311" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R311" t="n">
         <v>13</v>
@@ -19796,6 +23826,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>64</v>
+      </c>
       <c r="Q312" t="b">
         <v>0</v>
       </c>
@@ -19858,6 +23901,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>40</v>
+      </c>
       <c r="Q313" t="b">
         <v>0</v>
       </c>
@@ -19920,6 +23976,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P314" t="n">
+        <v>46</v>
+      </c>
       <c r="Q314" t="b">
         <v>0</v>
       </c>
@@ -19982,6 +24051,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P315" t="n">
+        <v>63</v>
+      </c>
       <c r="Q315" t="b">
         <v>0</v>
       </c>
@@ -20044,6 +24126,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P316" t="n">
+        <v>35</v>
+      </c>
       <c r="Q316" t="b">
         <v>0</v>
       </c>
@@ -20106,6 +24201,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P317" t="n">
+        <v>41</v>
+      </c>
       <c r="Q317" t="b">
         <v>0</v>
       </c>
@@ -20168,8 +24276,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P318" t="n">
+        <v>65</v>
+      </c>
       <c r="Q318" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R318" t="n">
         <v>13</v>
@@ -20230,6 +24351,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P319" t="n">
+        <v>59</v>
+      </c>
       <c r="Q319" t="b">
         <v>0</v>
       </c>
@@ -20292,6 +24426,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P320" t="n">
+        <v>36</v>
+      </c>
       <c r="Q320" t="b">
         <v>0</v>
       </c>
@@ -20354,6 +24501,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>40</v>
+      </c>
       <c r="Q321" t="b">
         <v>0</v>
       </c>
@@ -20416,6 +24576,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P322" t="n">
+        <v>33</v>
+      </c>
       <c r="Q322" t="b">
         <v>0</v>
       </c>
@@ -20478,8 +24651,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P323" t="n">
+        <v>40</v>
+      </c>
       <c r="Q323" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R323" t="n">
         <v>13</v>
@@ -20540,6 +24726,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P324" t="n">
+        <v>46</v>
+      </c>
       <c r="Q324" t="b">
         <v>0</v>
       </c>
@@ -20602,6 +24801,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P325" t="n">
+        <v>47</v>
+      </c>
       <c r="Q325" t="b">
         <v>0</v>
       </c>
@@ -20664,6 +24876,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>64</v>
+      </c>
       <c r="Q326" t="b">
         <v>0</v>
       </c>
@@ -20726,6 +24951,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P327" t="n">
+        <v>61</v>
+      </c>
       <c r="Q327" t="b">
         <v>0</v>
       </c>
@@ -20788,6 +25026,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P328" t="n">
+        <v>50</v>
+      </c>
       <c r="Q328" t="b">
         <v>0</v>
       </c>
@@ -20850,6 +25101,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P329" t="n">
+        <v>41</v>
+      </c>
       <c r="Q329" t="b">
         <v>0</v>
       </c>
@@ -20912,6 +25176,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P330" t="n">
+        <v>43</v>
+      </c>
       <c r="Q330" t="b">
         <v>0</v>
       </c>
@@ -20974,6 +25251,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P331" t="n">
+        <v>52</v>
+      </c>
       <c r="Q331" t="b">
         <v>0</v>
       </c>
@@ -21036,6 +25326,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P332" t="n">
+        <v>41</v>
+      </c>
       <c r="Q332" t="b">
         <v>0</v>
       </c>
@@ -21098,6 +25401,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P333" t="n">
+        <v>59</v>
+      </c>
       <c r="Q333" t="b">
         <v>0</v>
       </c>
@@ -21160,6 +25476,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P334" t="n">
+        <v>37</v>
+      </c>
       <c r="Q334" t="b">
         <v>0</v>
       </c>
@@ -21222,6 +25551,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P335" t="n">
+        <v>62</v>
+      </c>
       <c r="Q335" t="b">
         <v>0</v>
       </c>
@@ -21284,6 +25626,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P336" t="n">
+        <v>39</v>
+      </c>
       <c r="Q336" t="b">
         <v>0</v>
       </c>
@@ -21346,8 +25701,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P337" t="n">
+        <v>48</v>
+      </c>
       <c r="Q337" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R337" t="n">
         <v>13</v>
@@ -21408,6 +25776,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P338" t="n">
+        <v>60</v>
+      </c>
       <c r="Q338" t="b">
         <v>0</v>
       </c>
@@ -21470,6 +25851,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P339" t="n">
+        <v>61</v>
+      </c>
       <c r="Q339" t="b">
         <v>0</v>
       </c>
@@ -21532,6 +25926,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P340" t="n">
+        <v>50</v>
+      </c>
       <c r="Q340" t="b">
         <v>0</v>
       </c>
@@ -21594,6 +26001,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P341" t="n">
+        <v>51</v>
+      </c>
       <c r="Q341" t="b">
         <v>0</v>
       </c>
@@ -21656,6 +26076,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P342" t="n">
+        <v>55</v>
+      </c>
       <c r="Q342" t="b">
         <v>0</v>
       </c>
@@ -21718,8 +26151,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P343" t="n">
+        <v>57</v>
+      </c>
       <c r="Q343" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R343" t="n">
         <v>13</v>
@@ -21780,6 +26226,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P344" t="n">
+        <v>47</v>
+      </c>
       <c r="Q344" t="b">
         <v>0</v>
       </c>
@@ -21842,6 +26301,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P345" t="n">
+        <v>60</v>
+      </c>
       <c r="Q345" t="b">
         <v>0</v>
       </c>
@@ -21904,6 +26376,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P346" t="n">
+        <v>59</v>
+      </c>
       <c r="Q346" t="b">
         <v>0</v>
       </c>
@@ -21966,6 +26451,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P347" t="n">
+        <v>45</v>
+      </c>
       <c r="Q347" t="b">
         <v>0</v>
       </c>
@@ -22028,6 +26526,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P348" t="n">
+        <v>46</v>
+      </c>
       <c r="Q348" t="b">
         <v>0</v>
       </c>
@@ -22090,6 +26601,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P349" t="n">
+        <v>69</v>
+      </c>
       <c r="Q349" t="b">
         <v>0</v>
       </c>
@@ -22152,6 +26676,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P350" t="n">
+        <v>70</v>
+      </c>
       <c r="Q350" t="b">
         <v>0</v>
       </c>
@@ -22214,6 +26751,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P351" t="n">
+        <v>30</v>
+      </c>
       <c r="Q351" t="b">
         <v>0</v>
       </c>
@@ -22276,6 +26826,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P352" t="n">
+        <v>51</v>
+      </c>
       <c r="Q352" t="b">
         <v>0</v>
       </c>
@@ -22338,6 +26901,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P353" t="n">
+        <v>43</v>
+      </c>
       <c r="Q353" t="b">
         <v>0</v>
       </c>
@@ -22400,6 +26976,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P354" t="n">
+        <v>51</v>
+      </c>
       <c r="Q354" t="b">
         <v>0</v>
       </c>
@@ -22462,8 +27051,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P355" t="n">
+        <v>44</v>
+      </c>
       <c r="Q355" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R355" t="n">
         <v>13</v>
@@ -22524,6 +27126,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P356" t="n">
+        <v>65</v>
+      </c>
       <c r="Q356" t="b">
         <v>0</v>
       </c>
@@ -22586,6 +27201,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P357" t="n">
+        <v>37</v>
+      </c>
       <c r="Q357" t="b">
         <v>0</v>
       </c>
@@ -22648,6 +27276,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P358" t="n">
+        <v>43</v>
+      </c>
       <c r="Q358" t="b">
         <v>0</v>
       </c>
@@ -22710,6 +27351,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P359" t="n">
+        <v>42</v>
+      </c>
       <c r="Q359" t="b">
         <v>0</v>
       </c>
@@ -22772,6 +27426,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P360" t="n">
+        <v>43</v>
+      </c>
       <c r="Q360" t="b">
         <v>0</v>
       </c>
@@ -22834,6 +27501,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P361" t="n">
+        <v>44</v>
+      </c>
       <c r="Q361" t="b">
         <v>0</v>
       </c>
@@ -22896,6 +27576,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P362" t="n">
+        <v>47</v>
+      </c>
       <c r="Q362" t="b">
         <v>0</v>
       </c>
@@ -22958,8 +27651,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P363" t="n">
+        <v>62</v>
+      </c>
       <c r="Q363" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R363" t="n">
         <v>13</v>
@@ -23020,6 +27726,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P364" t="n">
+        <v>52</v>
+      </c>
       <c r="Q364" t="b">
         <v>0</v>
       </c>
@@ -23082,6 +27801,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P365" t="n">
+        <v>63</v>
+      </c>
       <c r="Q365" t="b">
         <v>0</v>
       </c>
@@ -23144,6 +27876,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P366" t="n">
+        <v>38</v>
+      </c>
       <c r="Q366" t="b">
         <v>0</v>
       </c>
@@ -23206,6 +27951,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P367" t="n">
+        <v>72</v>
+      </c>
       <c r="Q367" t="b">
         <v>0</v>
       </c>
@@ -23268,6 +28026,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P368" t="n">
+        <v>54</v>
+      </c>
       <c r="Q368" t="b">
         <v>0</v>
       </c>
@@ -23330,6 +28101,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P369" t="n">
+        <v>61</v>
+      </c>
       <c r="Q369" t="b">
         <v>0</v>
       </c>
@@ -23392,6 +28176,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P370" t="n">
+        <v>64</v>
+      </c>
       <c r="Q370" t="b">
         <v>0</v>
       </c>
@@ -23454,6 +28251,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P371" t="n">
+        <v>41</v>
+      </c>
       <c r="Q371" t="b">
         <v>0</v>
       </c>
@@ -23516,6 +28326,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P372" t="n">
+        <v>40</v>
+      </c>
       <c r="Q372" t="b">
         <v>0</v>
       </c>
@@ -23578,6 +28401,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P373" t="n">
+        <v>46</v>
+      </c>
       <c r="Q373" t="b">
         <v>0</v>
       </c>
@@ -23640,6 +28476,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P374" t="n">
+        <v>51</v>
+      </c>
       <c r="Q374" t="b">
         <v>0</v>
       </c>
@@ -23702,8 +28551,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P375" t="n">
+        <v>41</v>
+      </c>
       <c r="Q375" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R375" t="n">
         <v>13</v>
@@ -23764,6 +28626,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P376" t="n">
+        <v>30</v>
+      </c>
       <c r="Q376" t="b">
         <v>0</v>
       </c>
@@ -23826,6 +28701,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P377" t="n">
+        <v>69</v>
+      </c>
       <c r="Q377" t="b">
         <v>0</v>
       </c>
@@ -23888,6 +28776,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P378" t="n">
+        <v>43</v>
+      </c>
       <c r="Q378" t="b">
         <v>0</v>
       </c>
@@ -23950,6 +28851,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P379" t="n">
+        <v>48</v>
+      </c>
       <c r="Q379" t="b">
         <v>0</v>
       </c>
@@ -24012,6 +28926,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P380" t="n">
+        <v>49</v>
+      </c>
       <c r="Q380" t="b">
         <v>0</v>
       </c>
@@ -24074,6 +29001,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P381" t="n">
+        <v>66</v>
+      </c>
       <c r="Q381" t="b">
         <v>0</v>
       </c>
@@ -24136,6 +29076,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P382" t="n">
+        <v>41</v>
+      </c>
       <c r="Q382" t="b">
         <v>0</v>
       </c>
@@ -24198,8 +29151,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P383" t="n">
+        <v>67</v>
+      </c>
       <c r="Q383" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R383" t="n">
         <v>13</v>
@@ -24260,6 +29226,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P384" t="n">
+        <v>60</v>
+      </c>
       <c r="Q384" t="b">
         <v>0</v>
       </c>
@@ -24322,6 +29301,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P385" t="n">
+        <v>36</v>
+      </c>
       <c r="Q385" t="b">
         <v>0</v>
       </c>
@@ -24384,6 +29376,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P386" t="n">
+        <v>37</v>
+      </c>
       <c r="Q386" t="b">
         <v>0</v>
       </c>
@@ -24446,6 +29451,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P387" t="n">
+        <v>53</v>
+      </c>
       <c r="Q387" t="b">
         <v>0</v>
       </c>
@@ -24508,8 +29526,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P388" t="n">
+        <v>57</v>
+      </c>
       <c r="Q388" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R388" t="n">
         <v>13</v>
@@ -24570,8 +29601,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P389" t="n">
+        <v>68</v>
+      </c>
       <c r="Q389" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R389" t="n">
         <v>13</v>
@@ -24632,6 +29676,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P390" t="n">
+        <v>62</v>
+      </c>
       <c r="Q390" t="b">
         <v>0</v>
       </c>
@@ -24694,6 +29751,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P391" t="n">
+        <v>65</v>
+      </c>
       <c r="Q391" t="b">
         <v>0</v>
       </c>
@@ -24756,6 +29826,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P392" t="n">
+        <v>62</v>
+      </c>
       <c r="Q392" t="b">
         <v>0</v>
       </c>
@@ -24818,6 +29901,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P393" t="n">
+        <v>48</v>
+      </c>
       <c r="Q393" t="b">
         <v>0</v>
       </c>
@@ -24880,6 +29976,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P394" t="n">
+        <v>34</v>
+      </c>
       <c r="Q394" t="b">
         <v>0</v>
       </c>
@@ -24942,8 +30051,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P395" t="n">
+        <v>50</v>
+      </c>
       <c r="Q395" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R395" t="n">
         <v>13</v>
@@ -25004,6 +30126,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P396" t="n">
+        <v>41</v>
+      </c>
       <c r="Q396" t="b">
         <v>0</v>
       </c>
@@ -25066,6 +30201,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P397" t="n">
+        <v>27</v>
+      </c>
       <c r="Q397" t="b">
         <v>0</v>
       </c>
@@ -25128,6 +30276,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P398" t="n">
+        <v>55</v>
+      </c>
       <c r="Q398" t="b">
         <v>0</v>
       </c>
@@ -25190,8 +30351,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P399" t="n">
+        <v>48</v>
+      </c>
       <c r="Q399" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R399" t="n">
         <v>13</v>
@@ -25252,6 +30426,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P400" t="n">
+        <v>66</v>
+      </c>
       <c r="Q400" t="b">
         <v>0</v>
       </c>
@@ -25314,6 +30501,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P401" t="n">
+        <v>34</v>
+      </c>
       <c r="Q401" t="b">
         <v>0</v>
       </c>
@@ -25376,6 +30576,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P402" t="n">
+        <v>60</v>
+      </c>
       <c r="Q402" t="b">
         <v>0</v>
       </c>
@@ -25438,6 +30651,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P403" t="n">
+        <v>41</v>
+      </c>
       <c r="Q403" t="b">
         <v>0</v>
       </c>
@@ -25500,8 +30726,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P404" t="n">
+        <v>48</v>
+      </c>
       <c r="Q404" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R404" t="n">
         <v>13</v>
@@ -25562,6 +30801,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P405" t="n">
+        <v>58</v>
+      </c>
       <c r="Q405" t="b">
         <v>0</v>
       </c>
@@ -25624,6 +30876,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P406" t="n">
+        <v>34</v>
+      </c>
       <c r="Q406" t="b">
         <v>0</v>
       </c>
@@ -25686,6 +30951,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P407" t="n">
+        <v>35</v>
+      </c>
       <c r="Q407" t="b">
         <v>0</v>
       </c>
@@ -25748,6 +31026,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P408" t="n">
+        <v>41</v>
+      </c>
       <c r="Q408" t="b">
         <v>0</v>
       </c>
@@ -25810,8 +31101,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P409" t="n">
+        <v>40</v>
+      </c>
       <c r="Q409" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R409" t="n">
         <v>13</v>
@@ -25872,6 +31176,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P410" t="n">
+        <v>41</v>
+      </c>
       <c r="Q410" t="b">
         <v>0</v>
       </c>
@@ -25934,6 +31251,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P411" t="n">
+        <v>37</v>
+      </c>
       <c r="Q411" t="b">
         <v>0</v>
       </c>
@@ -25996,6 +31326,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P412" t="n">
+        <v>48</v>
+      </c>
       <c r="Q412" t="b">
         <v>0</v>
       </c>
@@ -26058,6 +31401,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P413" t="n">
+        <v>40</v>
+      </c>
       <c r="Q413" t="b">
         <v>0</v>
       </c>
@@ -26120,8 +31476,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P414" t="n">
+        <v>84</v>
+      </c>
       <c r="Q414" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R414" t="n">
         <v>13</v>
@@ -26182,8 +31551,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P415" t="n">
+        <v>50</v>
+      </c>
       <c r="Q415" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R415" t="n">
         <v>13</v>
@@ -26244,6 +31626,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P416" t="n">
+        <v>56</v>
+      </c>
       <c r="Q416" t="b">
         <v>0</v>
       </c>
@@ -26306,6 +31701,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P417" t="n">
+        <v>45</v>
+      </c>
       <c r="Q417" t="b">
         <v>0</v>
       </c>
@@ -26368,6 +31776,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P418" t="n">
+        <v>47</v>
+      </c>
       <c r="Q418" t="b">
         <v>0</v>
       </c>
@@ -26430,6 +31851,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P419" t="n">
+        <v>34</v>
+      </c>
       <c r="Q419" t="b">
         <v>0</v>
       </c>
@@ -26492,6 +31926,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P420" t="n">
+        <v>32</v>
+      </c>
       <c r="Q420" t="b">
         <v>0</v>
       </c>
@@ -26554,6 +32001,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P421" t="n">
+        <v>35</v>
+      </c>
       <c r="Q421" t="b">
         <v>0</v>
       </c>
@@ -26616,6 +32076,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P422" t="n">
+        <v>42</v>
+      </c>
       <c r="Q422" t="b">
         <v>0</v>
       </c>
@@ -26678,6 +32151,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P423" t="n">
+        <v>40</v>
+      </c>
       <c r="Q423" t="b">
         <v>0</v>
       </c>
@@ -26740,6 +32226,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P424" t="n">
+        <v>56</v>
+      </c>
       <c r="Q424" t="b">
         <v>0</v>
       </c>
@@ -26802,6 +32301,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P425" t="n">
+        <v>62</v>
+      </c>
       <c r="Q425" t="b">
         <v>0</v>
       </c>
@@ -26864,6 +32376,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P426" t="n">
+        <v>55</v>
+      </c>
       <c r="Q426" t="b">
         <v>0</v>
       </c>
@@ -26926,6 +32451,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P427" t="n">
+        <v>62</v>
+      </c>
       <c r="Q427" t="b">
         <v>0</v>
       </c>
@@ -26988,6 +32526,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P428" t="n">
+        <v>56</v>
+      </c>
       <c r="Q428" t="b">
         <v>0</v>
       </c>
@@ -27050,8 +32601,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P429" t="n">
+        <v>60</v>
+      </c>
       <c r="Q429" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R429" t="n">
         <v>13</v>
@@ -27112,6 +32676,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P430" t="n">
+        <v>47</v>
+      </c>
       <c r="Q430" t="b">
         <v>0</v>
       </c>
@@ -27148,7 +32725,7 @@
         <v>8025</v>
       </c>
       <c r="F431" t="n">
-        <v>24.70294896263</v>
+        <v>24.70294896</v>
       </c>
       <c r="G431" t="n">
         <v>3</v>
@@ -27173,6 +32750,19 @@
         <is>
           <t>CPM</t>
         </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P431" t="n">
+        <v>41</v>
       </c>
       <c r="Q431" t="b">
         <v>0</v>
@@ -27236,6 +32826,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P432" t="n">
+        <v>50</v>
+      </c>
       <c r="Q432" t="b">
         <v>0</v>
       </c>
@@ -27298,6 +32901,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P433" t="n">
+        <v>69</v>
+      </c>
       <c r="Q433" t="b">
         <v>0</v>
       </c>
@@ -27360,6 +32976,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P434" t="n">
+        <v>45</v>
+      </c>
       <c r="Q434" t="b">
         <v>0</v>
       </c>
@@ -27422,6 +33051,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P435" t="n">
+        <v>66</v>
+      </c>
       <c r="Q435" t="b">
         <v>0</v>
       </c>
@@ -27484,6 +33126,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P436" t="n">
+        <v>78</v>
+      </c>
       <c r="Q436" t="b">
         <v>0</v>
       </c>
@@ -27546,6 +33201,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P437" t="n">
+        <v>61</v>
+      </c>
       <c r="Q437" t="b">
         <v>0</v>
       </c>
@@ -27608,6 +33276,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P438" t="n">
+        <v>38</v>
+      </c>
       <c r="Q438" t="b">
         <v>0</v>
       </c>
@@ -27670,6 +33351,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P439" t="n">
+        <v>27</v>
+      </c>
       <c r="Q439" t="b">
         <v>0</v>
       </c>
@@ -27732,6 +33426,19 @@
           <t>HiSP</t>
         </is>
       </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P440" t="n">
+        <v>44</v>
+      </c>
       <c r="Q440" t="b">
         <v>0</v>
       </c>
@@ -27794,6 +33501,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P441" t="n">
+        <v>33</v>
+      </c>
       <c r="Q441" t="b">
         <v>0</v>
       </c>
@@ -27856,6 +33576,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P442" t="n">
+        <v>38</v>
+      </c>
       <c r="Q442" t="b">
         <v>0</v>
       </c>
@@ -27918,8 +33651,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P443" t="n">
+        <v>60</v>
+      </c>
       <c r="Q443" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R443" t="n">
         <v>13</v>
@@ -27980,6 +33726,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P444" t="n">
+        <v>49</v>
+      </c>
       <c r="Q444" t="b">
         <v>0</v>
       </c>
@@ -28042,6 +33801,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P445" t="n">
+        <v>56</v>
+      </c>
       <c r="Q445" t="b">
         <v>0</v>
       </c>
@@ -28104,8 +33876,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P446" t="n">
+        <v>58</v>
+      </c>
       <c r="Q446" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R446" t="n">
         <v>13</v>
@@ -28166,6 +33951,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P447" t="n">
+        <v>56</v>
+      </c>
       <c r="Q447" t="b">
         <v>0</v>
       </c>
@@ -28228,6 +34026,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P448" t="n">
+        <v>66</v>
+      </c>
       <c r="Q448" t="b">
         <v>0</v>
       </c>
@@ -28290,6 +34101,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P449" t="n">
+        <v>36</v>
+      </c>
       <c r="Q449" t="b">
         <v>0</v>
       </c>
@@ -28352,6 +34176,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P450" t="n">
+        <v>47</v>
+      </c>
       <c r="Q450" t="b">
         <v>0</v>
       </c>
@@ -28414,6 +34251,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P451" t="n">
+        <v>58</v>
+      </c>
       <c r="Q451" t="b">
         <v>0</v>
       </c>
@@ -28476,6 +34326,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P452" t="n">
+        <v>37</v>
+      </c>
       <c r="Q452" t="b">
         <v>0</v>
       </c>
@@ -28538,6 +34401,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P453" t="n">
+        <v>43</v>
+      </c>
       <c r="Q453" t="b">
         <v>0</v>
       </c>
@@ -28600,6 +34476,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P454" t="n">
+        <v>34</v>
+      </c>
       <c r="Q454" t="b">
         <v>0</v>
       </c>
@@ -28662,6 +34551,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P455" t="n">
+        <v>35</v>
+      </c>
       <c r="Q455" t="b">
         <v>0</v>
       </c>
@@ -28724,6 +34626,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P456" t="n">
+        <v>57</v>
+      </c>
       <c r="Q456" t="b">
         <v>0</v>
       </c>
@@ -28786,8 +34701,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P457" t="n">
+        <v>52</v>
+      </c>
       <c r="Q457" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R457" t="n">
         <v>13</v>
@@ -28848,6 +34776,19 @@
           <t>HLP</t>
         </is>
       </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P458" t="n">
+        <v>64</v>
+      </c>
       <c r="Q458" t="b">
         <v>0</v>
       </c>
@@ -28910,6 +34851,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P459" t="n">
+        <v>34</v>
+      </c>
       <c r="Q459" t="b">
         <v>0</v>
       </c>
@@ -28971,6 +34925,19 @@
         <is>
           <t>NCP</t>
         </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P460" t="n">
+        <v>38</v>
       </c>
       <c r="Q460" t="b">
         <v>0</v>

--- a/static/data/exports/Retro_HP_AE_2012.xlsx
+++ b/static/data/exports/Retro_HP_AE_2012.xlsx
@@ -2340,11 +2340,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E26" t="n">
         <v>960</v>
@@ -7740,11 +7740,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E98" t="n">
         <v>828</v>
@@ -10440,11 +10440,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E134" t="n">
         <v>402</v>
@@ -13740,11 +13740,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E178" t="n">
         <v>474</v>
@@ -15690,11 +15690,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E204" t="n">
         <v>1094</v>
@@ -16515,11 +16515,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E215" t="n">
         <v>2056</v>
@@ -18465,11 +18465,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E241" t="n">
         <v>600</v>
@@ -20565,11 +20565,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E269" t="n">
         <v>1368</v>
@@ -23490,11 +23490,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E308" t="n">
         <v>1377</v>
@@ -26415,11 +26415,11 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E347" t="n">
         <v>2981</v>
@@ -28665,11 +28665,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E377" t="n">
         <v>837</v>
@@ -30090,11 +30090,11 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E396" t="n">
         <v>1531</v>
@@ -30765,11 +30765,11 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E405" t="n">
         <v>1346</v>
@@ -31590,11 +31590,11 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E416" t="n">
         <v>10379</v>
@@ -32190,11 +32190,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E424" t="n">
         <v>4823</v>
@@ -32715,11 +32715,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E431" t="n">
         <v>8025</v>
